--- a/TriToDo.xlsx
+++ b/TriToDo.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30324"/>
   <workbookPr showInkAnnotation="0"/>
-  <xr:revisionPtr revIDLastSave="176" documentId="7_{046A3801-B870-2144-A3DE-C380BD0DB075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FE636E9-D0F3-4FDC-A82C-9F4AA81CBC31}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="7_{046A3801-B870-2144-A3DE-C380BD0DB075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{705863EE-8EE7-4D55-8490-B536C77F0294}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="To Do" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="90">
   <si>
     <t>List</t>
   </si>
@@ -62,21 +62,75 @@
     <t>Talk to the pool</t>
   </si>
   <si>
+    <t>Prep aid station</t>
+  </si>
+  <si>
     <t>Cups</t>
   </si>
   <si>
     <t>Get cloth for small table</t>
   </si>
   <si>
+    <t>Shop with Chris</t>
+  </si>
+  <si>
     <t>Ice</t>
   </si>
   <si>
+    <t>Oranges</t>
+  </si>
+  <si>
     <t>Chalk</t>
   </si>
   <si>
+    <t>Prep</t>
+  </si>
+  <si>
+    <t>Welcome to the first edition of Mega House Tri a Try! This is your chance to try a triathlon, practice for an upcoming race, or just have fun with friends. Be safe and see you on the course :)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The day will start at Mega House at 9am - arrive early! Atheletes must check-in upon arrival and setup their T2 (transition from bike to run) in the garage. A mandatory race briefing will happen inside between 9:30-9:40. </t>
+  </si>
+  <si>
+    <t>At 9:40 athelets will travel to the pool via bike with the option to place other gear in a vehicle that will meet them at the pool.</t>
+  </si>
+  <si>
+    <t>The swim will occure during the public lane swim session at Rengstorff pool. Depending on how busy the pool is, athlete will select a lane corresponding to their expected speed and either all begin simultaneously (mass start) or be split into heats approximetly 15 minutes apart. In either case be mindful of other patrons and follow directions of pool staff &amp; lilfeguards.</t>
+  </si>
+  <si>
+    <t>The swim distance is 750m (30 laps). Athletes must track their own progress via smart watch or counting laps.</t>
+  </si>
+  <si>
+    <t>Athletes will exit the water and make their way outside the recreation complex to transition to the bike segment. Althetes have the option to stop in the changing room before heading to the bike.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once in transition, athletes must equip their helmet before heading out onto the bike course. </t>
+  </si>
+  <si>
+    <t>The bike course is a 20km point-to-point ride from Rengstorff pool to Mega House, extending south through Loyola. This portion is self-supported meaning the athlete must carry their own nutrition and hydration required for the duration of the bike.</t>
+  </si>
+  <si>
+    <t>The course will be partially marked with chalk arrows on the ground and small signage.It is the athletes responsibility to stay on course.</t>
+  </si>
+  <si>
     <t>If you're worried about getting lost, carry your phone. Use the RidewithGPS app with location services turned on to overlay your location on the course map.</t>
   </si>
   <si>
+    <t>The course follows public roads and paths - follow traffic laws and exercise caution at all times!</t>
+  </si>
+  <si>
+    <t>Athletes will disembark in the Mega House driveway, pass off their bike to a volunteer, and equipe their running gear in the garage.</t>
+  </si>
+  <si>
+    <t>The run consists of a 2 lap clockwise course starting and ending at the Mega House.</t>
+  </si>
+  <si>
+    <t>The course will be partially marked with chalk arrows on the ground.</t>
+  </si>
+  <si>
+    <t>All segments of the race will be timed and available for viewing after the race.</t>
+  </si>
+  <si>
     <t>Athlete schedule</t>
   </si>
   <si>
@@ -107,9 +161,15 @@
     <t>Mega House</t>
   </si>
   <si>
+    <t xml:space="preserve">Check-in. T2 setup guidance. Athlete briefing. </t>
+  </si>
+  <si>
     <t>9:00-9:30</t>
   </si>
   <si>
+    <t>Check-in. T2 setup guidance.</t>
+  </si>
+  <si>
     <t>Swim</t>
   </si>
   <si>
@@ -131,9 +191,15 @@
     <t>Pool - T1</t>
   </si>
   <si>
+    <t>T2 setup guidance</t>
+  </si>
+  <si>
     <t>9:40-11:00</t>
   </si>
   <si>
+    <t>Timing</t>
+  </si>
+  <si>
     <t>T1</t>
   </si>
   <si>
@@ -149,7 +215,13 @@
     <t>Pool - deck</t>
   </si>
   <si>
+    <t xml:space="preserve">Start prep. Athlete timing. </t>
+  </si>
+  <si>
     <t>11:00-end</t>
+  </si>
+  <si>
+    <t>Aid station setup and operation</t>
   </si>
   <si>
     <t>Bike</t>
@@ -294,7 +366,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -662,23 +734,32 @@
       <c r="D4" t="s">
         <v>7</v>
       </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -688,12 +769,87 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2FF392-66C0-4066-9B41-8A5DC44BE6F2}">
-  <dimension ref="B5"/>
+  <dimension ref="B2:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -703,342 +859,370 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38ADB62B-45DE-4608-B107-57B3598BB926}">
-  <dimension ref="B2:X12"/>
+  <dimension ref="B2:Y12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="19" max="19" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:24">
+    <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="2:25">
+      <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3">
+        <v>8.5</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3">
+        <v>22.5</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
+      </c>
+      <c r="W3" t="s">
+        <v>44</v>
+      </c>
+      <c r="X3">
+        <v>11.25</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="2:25">
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="S4" t="s">
+        <v>54</v>
+      </c>
+      <c r="T4">
+        <v>8</v>
+      </c>
+      <c r="W4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:25">
+      <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5">
+        <v>35</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>63</v>
+      </c>
+      <c r="S5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5">
+        <v>80</v>
+      </c>
+      <c r="U5" t="s">
+        <v>64</v>
+      </c>
+      <c r="W5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X5">
+        <v>40</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="2:25">
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6">
+        <v>0.5</v>
+      </c>
+      <c r="S6" t="s">
+        <v>69</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="W6" t="s">
+        <v>69</v>
+      </c>
+      <c r="X6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25">
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="2:24">
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="Q7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S7" t="s">
+        <v>72</v>
+      </c>
+      <c r="T7">
+        <v>60</v>
+      </c>
+      <c r="U7" t="s">
+        <v>74</v>
+      </c>
+      <c r="W7" t="s">
+        <v>72</v>
+      </c>
+      <c r="X7">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3">
-        <v>8.5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3">
-        <v>22.5</v>
-      </c>
-      <c r="T3" t="s">
-        <v>26</v>
-      </c>
-      <c r="V3" t="s">
-        <v>24</v>
-      </c>
-      <c r="W3">
-        <v>11.25</v>
-      </c>
-      <c r="X3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:24">
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="R4" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4">
-        <v>8</v>
-      </c>
-      <c r="V4" t="s">
-        <v>32</v>
-      </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:24">
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5">
-        <v>35</v>
-      </c>
-      <c r="P5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5">
+      <c r="Y7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="2:25">
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P8" s="4">
+        <f>SUM(P3:P7)</f>
+        <v>63</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="T8" s="4">
+        <f>SUM(T3:T7)</f>
+        <v>173.5</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="X8" s="4">
+        <f>SUM(X3:X7)</f>
+        <v>74.75</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25">
+      <c r="B9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T5" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" t="s">
-        <v>38</v>
-      </c>
-      <c r="W5">
-        <v>40</v>
-      </c>
-      <c r="X5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="2:24">
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6">
-        <v>0.5</v>
-      </c>
-      <c r="R6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6">
-        <v>3</v>
-      </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:24">
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7">
-        <v>18</v>
-      </c>
-      <c r="P7" t="s">
-        <v>49</v>
-      </c>
-      <c r="R7" t="s">
-        <v>48</v>
-      </c>
-      <c r="S7">
-        <v>60</v>
-      </c>
-      <c r="T7" t="s">
-        <v>50</v>
-      </c>
-      <c r="V7" t="s">
-        <v>48</v>
-      </c>
-      <c r="W7">
-        <v>22</v>
-      </c>
-      <c r="X7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="2:24">
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="O8" s="4">
-        <f>SUM(O3:O7)</f>
-        <v>63</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="S8" s="4">
-        <f>SUM(S3:S7)</f>
-        <v>173.5</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="W8" s="4">
-        <f>SUM(W3:W7)</f>
-        <v>74.75</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="2:24">
-      <c r="B9" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="C9" t="s">
-        <v>57</v>
-      </c>
-      <c r="S9" s="5">
-        <f>S8/60</f>
+        <v>81</v>
+      </c>
+      <c r="T9" s="5">
+        <f>T8/60</f>
         <v>2.8916666666666666</v>
       </c>
-      <c r="T9" t="s">
-        <v>58</v>
-      </c>
-      <c r="W9" s="5">
-        <f>W8/60</f>
+      <c r="U9" t="s">
+        <v>82</v>
+      </c>
+      <c r="X9" s="5">
+        <f>X8/60</f>
         <v>1.2458333333333333</v>
       </c>
-      <c r="X9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="2:24">
+      <c r="Y9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25">
       <c r="B10" s="3" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
-      </c>
-      <c r="N10" t="s">
-        <v>61</v>
-      </c>
-      <c r="O10" s="2">
+        <v>84</v>
+      </c>
+      <c r="O10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" s="2">
         <v>0.48125000000000001</v>
       </c>
-      <c r="R10" t="s">
-        <v>61</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="S10" t="s">
+        <v>85</v>
+      </c>
+      <c r="T10" s="2">
         <v>0.55763888888888891</v>
       </c>
-      <c r="V10" t="s">
-        <v>61</v>
-      </c>
-      <c r="W10" s="2">
+      <c r="W10" t="s">
+        <v>85</v>
+      </c>
+      <c r="X10" s="2">
         <v>0.48958333333333331</v>
       </c>
     </row>
-    <row r="11" spans="2:24">
+    <row r="11" spans="2:25">
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="2:24">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25">
       <c r="B12" s="3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/TriToDo.xlsx
+++ b/TriToDo.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr showInkAnnotation="0"/>
-  <xr:revisionPtr revIDLastSave="238" documentId="7_{046A3801-B870-2144-A3DE-C380BD0DB075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{705863EE-8EE7-4D55-8490-B536C77F0294}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="7_{046A3801-B870-2144-A3DE-C380BD0DB075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DFE4FBB-F70E-4043-A84C-23B87A408722}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>List</t>
   </si>
@@ -68,19 +68,25 @@
     <t>Cups</t>
   </si>
   <si>
-    <t>Get cloth for small table</t>
-  </si>
-  <si>
     <t>Shop with Chris</t>
   </si>
   <si>
     <t>Ice</t>
   </si>
   <si>
+    <t>Chalk</t>
+  </si>
+  <si>
+    <t>Signs</t>
+  </si>
+  <si>
+    <t>Red sharpie</t>
+  </si>
+  <si>
     <t>Oranges</t>
   </si>
   <si>
-    <t>Chalk</t>
+    <t>Bananas</t>
   </si>
   <si>
     <t>Prep</t>
@@ -702,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476DD4CE-F6AA-BB45-AF65-18424309FB8F}">
-  <dimension ref="B2:F7"/>
+  <dimension ref="B2:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:6">
@@ -742,24 +748,38 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -774,82 +794,82 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -876,116 +896,116 @@
   <sheetData>
     <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="2:25">
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" t="s">
         <v>42</v>
       </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
       <c r="M3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P3">
         <v>8.5</v>
       </c>
       <c r="Q3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T3">
         <v>22.5</v>
       </c>
       <c r="U3" t="s">
+        <v>48</v>
+      </c>
+      <c r="W3" t="s">
         <v>46</v>
-      </c>
-      <c r="W3" t="s">
-        <v>44</v>
       </c>
       <c r="X3">
         <v>11.25</v>
       </c>
       <c r="Y3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="2:25">
       <c r="B4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" t="s">
         <v>52</v>
       </c>
-      <c r="L4" t="s">
-        <v>50</v>
-      </c>
       <c r="M4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P4">
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T4">
         <v>8</v>
       </c>
       <c r="W4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -993,87 +1013,87 @@
     </row>
     <row r="5" spans="2:25">
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P5">
         <v>35</v>
       </c>
       <c r="Q5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="S5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T5">
         <v>80</v>
       </c>
       <c r="U5" t="s">
+        <v>66</v>
+      </c>
+      <c r="W5" t="s">
         <v>64</v>
-      </c>
-      <c r="W5" t="s">
-        <v>62</v>
       </c>
       <c r="X5">
         <v>40</v>
       </c>
       <c r="Y5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="2:25">
       <c r="B6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P6">
         <v>0.5</v>
       </c>
       <c r="S6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="T6">
         <v>3</v>
       </c>
       <c r="W6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X6">
         <v>0.5</v>
@@ -1081,129 +1101,129 @@
     </row>
     <row r="7" spans="2:25">
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P7">
         <v>18</v>
       </c>
       <c r="Q7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="S7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T7">
         <v>60</v>
       </c>
       <c r="U7" t="s">
+        <v>76</v>
+      </c>
+      <c r="W7" t="s">
         <v>74</v>
-      </c>
-      <c r="W7" t="s">
-        <v>72</v>
       </c>
       <c r="X7">
         <v>22</v>
       </c>
       <c r="Y7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:25">
       <c r="B8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P8" s="4">
         <f>SUM(P3:P7)</f>
         <v>63</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T8" s="4">
         <f>SUM(T3:T7)</f>
         <v>173.5</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X8" s="4">
         <f>SUM(X3:X7)</f>
         <v>74.75</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="2:25">
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T9" s="5">
         <f>T8/60</f>
         <v>2.8916666666666666</v>
       </c>
       <c r="U9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X9" s="5">
         <f>X8/60</f>
         <v>1.2458333333333333</v>
       </c>
       <c r="Y9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="2:25">
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P10" s="2">
         <v>0.48125000000000001</v>
       </c>
       <c r="S10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="T10" s="2">
         <v>0.55763888888888891</v>
       </c>
       <c r="W10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="X10" s="2">
         <v>0.48958333333333331</v>
@@ -1211,18 +1231,18 @@
     </row>
     <row r="11" spans="2:25">
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="2:25">
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
